--- a/InputData/geoeng/DACD/Direct Air Capture Data.xlsx
+++ b/InputData/geoeng/DACD/Direct Air Capture Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\geoeng\DACD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\geoeng\DACD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B4DA15-A5FF-4D91-BA4E-A5CD251C9157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5139D15E-CB52-4E6B-A000-C9F7BE131494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -942,28 +942,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="47.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -971,97 +971,97 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>2021</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -1079,13 +1079,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C706B8D-FB10-40CA-B025-270C2E82347D}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.26953125" customWidth="1"/>
-    <col min="4" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="4" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>82</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>95</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>96</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>94</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>97</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>8.9285714285714274E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -1135,42 +1135,42 @@
         <v>0.3571428571428571</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>2020</v>
       </c>
       <c r="C16">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="D16">
         <v>2040</v>
@@ -1179,7 +1179,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1208,58 +1208,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H105"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.26953125" customWidth="1"/>
-    <col min="2" max="8" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="8" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -1270,7 +1270,7 @@
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>1</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1314,12 +1314,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>1</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
@@ -1352,17 +1352,17 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>1</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>2</v>
       </c>
@@ -1395,15 +1395,15 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>103</v>
       </c>
@@ -1414,15 +1414,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>2.3759999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
@@ -1459,27 +1459,27 @@
         <v>1.452</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>43</v>
       </c>
@@ -1491,27 +1491,27 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>2045</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>29</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74">
         <v>2045</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>32</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>27.071428571428573</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>33</v>
       </c>
@@ -1683,27 +1683,27 @@
         <v>2.8571428571428568</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>38</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>42</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>0.24237500000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>44</v>
       </c>
@@ -1752,7 +1752,7 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88">
         <v>2045</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>32</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>6.5614375000000003</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>33</v>
       </c>
@@ -1841,12 +1841,12 @@
         <v>0.69249999999999989</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93">
         <v>2045</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>46</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>6561437500</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -1935,32 +1935,32 @@
         <v>692499999.99999988</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>54</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>947086</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>72</v>
       </c>
@@ -1986,16 +1986,16 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.81640625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
-    <col min="3" max="24" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="26" max="35" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="24" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -2160,43 +2160,43 @@
       </c>
       <c r="O2" s="16" cm="1">
         <f t="array" ref="O2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!O1)</f>
-        <v>0</v>
+        <v>8116883.1168842316</v>
       </c>
       <c r="P2" s="16" cm="1">
         <f t="array" ref="P2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!P1)</f>
-        <v>8928571.4285736084</v>
+        <v>16233766.233766556</v>
       </c>
       <c r="Q2" s="16" cm="1">
         <f t="array" ref="Q2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!Q1)</f>
-        <v>17857142.857143402</v>
+        <v>24350649.35064888</v>
       </c>
       <c r="R2" s="16" cm="1">
         <f t="array" ref="R2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!R1)</f>
-        <v>26785714.28571701</v>
+        <v>32467532.467533112</v>
       </c>
       <c r="S2" s="16" cm="1">
         <f t="array" ref="S2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!S1)</f>
-        <v>35714285.714286804</v>
+        <v>40584415.584415436</v>
       </c>
       <c r="T2" s="16" cm="1">
         <f t="array" ref="T2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!T1)</f>
-        <v>44642857.142856598</v>
+        <v>48701298.701299667</v>
       </c>
       <c r="U2" s="16" cm="1">
         <f t="array" ref="U2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!U1)</f>
-        <v>53571428.571430206</v>
+        <v>56818181.818181992</v>
       </c>
       <c r="V2" s="16" cm="1">
         <f t="array" ref="V2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!V1)</f>
-        <v>62500000</v>
+        <v>64935064.935064316</v>
       </c>
       <c r="W2" s="16" cm="1">
         <f t="array" ref="W2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!W1)</f>
-        <v>71428571.428573608</v>
+        <v>73051948.051948547</v>
       </c>
       <c r="X2" s="16" cm="1">
         <f t="array" ref="X2">TREND('CDR potential'!$C$17:$D$17,'CDR potential'!$C$16:$D$16,'DACD-potential'!X1)</f>
-        <v>80357142.857143402</v>
+        <v>81168831.168830872</v>
       </c>
       <c r="Y2" s="16" cm="1">
         <f t="array" ref="Y2">TREND('CDR potential'!$D$17:$E$17,'CDR potential'!$D$16:$E$16,'DACD-potential'!Y1)</f>
@@ -2254,13 +2254,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>4236315.6780000003</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -3779,13 +3779,13 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
